--- a/data/primary_data/sieve.xlsx
+++ b/data/primary_data/sieve.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\PostGrad\BSc Hons\4ZOL509_Research\primary_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7803D6-43C8-43BB-A560-AD6BA6414331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B667D3-F6E8-4FC3-A283-798877B36FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5E08619-1D5D-4645-A7FE-EF3A7CFA34BE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="201">
   <si>
     <t>site</t>
   </si>
@@ -74,13 +74,562 @@
   </si>
   <si>
     <t>sieve_1mm</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>0.45</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>15.93</t>
+  </si>
+  <si>
+    <t>5.35</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>0.04</t>
+  </si>
+  <si>
+    <t>25.67</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>0.6</t>
+  </si>
+  <si>
+    <t>1.54</t>
+  </si>
+  <si>
+    <t>10.96</t>
+  </si>
+  <si>
+    <t>5.79</t>
+  </si>
+  <si>
+    <t>1.58</t>
+  </si>
+  <si>
+    <t>21.05</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>9.51</t>
+  </si>
+  <si>
+    <t>7.58</t>
+  </si>
+  <si>
+    <t>2.14</t>
+  </si>
+  <si>
+    <t>21.77</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>0.52</t>
+  </si>
+  <si>
+    <t>2.94</t>
+  </si>
+  <si>
+    <t>12.53</t>
+  </si>
+  <si>
+    <t>13.44</t>
+  </si>
+  <si>
+    <t>0.58</t>
+  </si>
+  <si>
+    <t>21.27</t>
+  </si>
+  <si>
+    <t>1.53</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>5.76</t>
+  </si>
+  <si>
+    <t>14.91</t>
+  </si>
+  <si>
+    <t>2.79</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>28.02</t>
+  </si>
+  <si>
+    <t>0.27</t>
+  </si>
+  <si>
+    <t>0.47</t>
+  </si>
+  <si>
+    <t>2.67</t>
+  </si>
+  <si>
+    <t>15.57</t>
+  </si>
+  <si>
+    <t>7.13</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>28.31</t>
+  </si>
+  <si>
+    <t>2.04</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>7.03</t>
+  </si>
+  <si>
+    <t>0.35</t>
+  </si>
+  <si>
+    <t>26.72</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>2.26</t>
+  </si>
+  <si>
+    <t>15.02</t>
+  </si>
+  <si>
+    <t>4.69</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>0.99</t>
+  </si>
+  <si>
+    <t>0.64</t>
+  </si>
+  <si>
+    <t>11.13</t>
+  </si>
+  <si>
+    <t>5.33</t>
+  </si>
+  <si>
+    <t>19.93</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>11.44</t>
+  </si>
+  <si>
+    <t>8.59</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>23.58</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>9.55</t>
+  </si>
+  <si>
+    <t>7.96</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>21.11</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>15.75</t>
+  </si>
+  <si>
+    <t>2.48</t>
+  </si>
+  <si>
+    <t>0.24</t>
+  </si>
+  <si>
+    <t>21.5</t>
+  </si>
+  <si>
+    <t>2.43</t>
+  </si>
+  <si>
+    <t>14.26</t>
+  </si>
+  <si>
+    <t>2.42</t>
+  </si>
+  <si>
+    <t>0.19</t>
+  </si>
+  <si>
+    <t>19.98</t>
+  </si>
+  <si>
+    <t>2.59</t>
+  </si>
+  <si>
+    <t>15.25</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>11.29</t>
+  </si>
+  <si>
+    <t>9.14</t>
+  </si>
+  <si>
+    <t>2.22</t>
+  </si>
+  <si>
+    <t>24.03</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>11.24</t>
+  </si>
+  <si>
+    <t>9.45</t>
+  </si>
+  <si>
+    <t>0.11</t>
+  </si>
+  <si>
+    <t>25.1</t>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>11.26</t>
+  </si>
+  <si>
+    <t>8.74</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>21.52</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>9.87</t>
+  </si>
+  <si>
+    <t>9.04</t>
+  </si>
+  <si>
+    <t>1.73</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>21.58</t>
+  </si>
+  <si>
+    <t>5.56</t>
+  </si>
+  <si>
+    <t>19.37</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>4.34</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>24.29</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>12.4</t>
+  </si>
+  <si>
+    <t>3.98</t>
+  </si>
+  <si>
+    <t>20.13</t>
+  </si>
+  <si>
+    <t>2.37</t>
+  </si>
+  <si>
+    <t>14.63</t>
+  </si>
+  <si>
+    <t>3.26</t>
+  </si>
+  <si>
+    <t>21.16</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>15.08</t>
+  </si>
+  <si>
+    <t>5.16</t>
+  </si>
+  <si>
+    <t>23.44</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>13.39</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>21.81</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>16.78</t>
+  </si>
+  <si>
+    <t>7.24</t>
+  </si>
+  <si>
+    <t>0.44</t>
+  </si>
+  <si>
+    <t>27.04</t>
+  </si>
+  <si>
+    <t>21.0</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>0.00</t>
+  </si>
+  <si>
+    <t>0.16</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>1.37</t>
+  </si>
+  <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>8.50</t>
+  </si>
+  <si>
+    <t>11.43</t>
+  </si>
+  <si>
+    <t>11.59</t>
+  </si>
+  <si>
+    <t>14.62</t>
+  </si>
+  <si>
+    <t>13.26</t>
+  </si>
+  <si>
+    <t>7.79</t>
+  </si>
+  <si>
+    <t>7.57</t>
+  </si>
+  <si>
+    <t>9.83</t>
+  </si>
+  <si>
+    <t>6.87</t>
+  </si>
+  <si>
+    <t>14.96</t>
+  </si>
+  <si>
+    <t>4.03</t>
+  </si>
+  <si>
+    <t>5.37</t>
+  </si>
+  <si>
+    <t>4.54</t>
+  </si>
+  <si>
+    <t>5.40</t>
+  </si>
+  <si>
+    <t>18.69</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>4.41</t>
+  </si>
+  <si>
+    <t>4.88</t>
+  </si>
+  <si>
+    <t>2.39</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>0.36</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>september</t>
+  </si>
+  <si>
+    <t>22.22</t>
+  </si>
+  <si>
+    <t>19.72</t>
+  </si>
+  <si>
+    <t>20.64</t>
+  </si>
+  <si>
+    <t>21.90</t>
+  </si>
+  <si>
+    <t>17.87</t>
+  </si>
+  <si>
+    <t>24.06</t>
+  </si>
+  <si>
+    <t>19.65</t>
+  </si>
+  <si>
+    <t>15.44</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +760,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -914,7 +1469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B1941EC-5D36-4969-84B5-0B119B8E4EB5}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -970,29 +1525,29 @@
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>0.39</v>
-      </c>
-      <c r="D2">
-        <v>0.45</v>
-      </c>
-      <c r="E2">
-        <v>2.23</v>
-      </c>
-      <c r="F2">
-        <v>15.93</v>
-      </c>
-      <c r="G2">
-        <v>5.35</v>
-      </c>
-      <c r="H2">
-        <v>1.3</v>
-      </c>
-      <c r="I2">
-        <v>0.04</v>
-      </c>
-      <c r="J2">
-        <v>25.67</v>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1008,29 +1563,29 @@
       <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3">
-        <v>0.09</v>
-      </c>
-      <c r="D3">
-        <v>0.6</v>
-      </c>
-      <c r="E3">
-        <v>1.54</v>
-      </c>
-      <c r="F3">
-        <v>10.96</v>
-      </c>
-      <c r="G3">
-        <v>5.79</v>
-      </c>
-      <c r="H3">
-        <v>1.58</v>
-      </c>
-      <c r="I3">
-        <v>0.09</v>
-      </c>
-      <c r="J3">
-        <v>21.05</v>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>32</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1046,29 +1601,29 @@
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>0.45</v>
-      </c>
-      <c r="D4">
-        <v>0.21</v>
-      </c>
-      <c r="E4">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F4">
-        <v>9.51</v>
-      </c>
-      <c r="G4">
-        <v>7.58</v>
-      </c>
-      <c r="H4">
-        <v>2.14</v>
-      </c>
-      <c r="I4">
-        <v>0.09</v>
-      </c>
-      <c r="J4">
-        <v>21.77</v>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1084,29 +1639,29 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>0.83</v>
-      </c>
-      <c r="D5">
-        <v>0.52</v>
-      </c>
-      <c r="E5">
-        <v>2.94</v>
-      </c>
-      <c r="F5">
-        <v>12.53</v>
-      </c>
-      <c r="G5">
-        <v>13.44</v>
-      </c>
-      <c r="H5">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I5">
-        <v>0.04</v>
-      </c>
-      <c r="J5">
-        <v>21.27</v>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1122,29 +1677,29 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6">
-        <v>1.53</v>
-      </c>
-      <c r="D6">
-        <v>1.7</v>
-      </c>
-      <c r="E6">
-        <v>5.76</v>
-      </c>
-      <c r="F6">
-        <v>14.91</v>
-      </c>
-      <c r="G6">
-        <v>2.79</v>
-      </c>
-      <c r="H6">
-        <v>0.26</v>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
-        <v>28.02</v>
+      <c r="J6" t="s">
+        <v>52</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1160,29 +1715,29 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>0.27</v>
-      </c>
-      <c r="D7">
-        <v>0.47</v>
-      </c>
-      <c r="E7">
-        <v>2.67</v>
-      </c>
-      <c r="F7">
-        <v>15.57</v>
-      </c>
-      <c r="G7">
-        <v>7.13</v>
-      </c>
-      <c r="H7">
-        <v>1.58</v>
-      </c>
-      <c r="I7">
-        <v>0.08</v>
-      </c>
-      <c r="J7">
-        <v>28.31</v>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" t="s">
+        <v>59</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1198,29 +1753,29 @@
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8">
-        <v>0.26</v>
-      </c>
-      <c r="D8">
-        <v>0.26</v>
-      </c>
-      <c r="E8">
-        <v>2.04</v>
-      </c>
-      <c r="F8">
-        <v>16.7</v>
-      </c>
-      <c r="G8">
-        <v>7.03</v>
-      </c>
-      <c r="H8">
-        <v>0.35</v>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" t="s">
+        <v>63</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8">
-        <v>26.72</v>
+      <c r="J8" t="s">
+        <v>64</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -1236,29 +1791,29 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9">
-        <v>0.81</v>
-      </c>
-      <c r="D9">
-        <v>0.37</v>
-      </c>
-      <c r="E9">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="F9">
-        <v>15.02</v>
-      </c>
-      <c r="G9">
-        <v>4.6900000000000004</v>
-      </c>
-      <c r="H9">
-        <v>0.39</v>
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9">
-        <v>25.4</v>
+      <c r="J9" t="s">
+        <v>70</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -1274,29 +1829,29 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10">
-        <v>0.99</v>
-      </c>
-      <c r="D10">
-        <v>0.64</v>
-      </c>
-      <c r="E10">
-        <v>2.14</v>
-      </c>
-      <c r="F10">
-        <v>11.13</v>
-      </c>
-      <c r="G10">
-        <v>5.33</v>
-      </c>
-      <c r="H10">
-        <v>0.26</v>
+      <c r="C10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10">
-        <v>19.93</v>
+      <c r="J10" t="s">
+        <v>75</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1312,29 +1867,29 @@
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11">
-        <v>0.04</v>
-      </c>
-      <c r="D11">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E11">
-        <v>1.91</v>
-      </c>
-      <c r="F11">
-        <v>11.44</v>
-      </c>
-      <c r="G11">
-        <v>8.59</v>
-      </c>
-      <c r="H11">
-        <v>1.72</v>
-      </c>
-      <c r="I11">
-        <v>0.09</v>
-      </c>
-      <c r="J11">
-        <v>23.58</v>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" t="s">
+        <v>81</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -1350,29 +1905,29 @@
       <c r="B12">
         <v>2</v>
       </c>
-      <c r="C12">
-        <v>0.21</v>
-      </c>
-      <c r="D12">
-        <v>0.47</v>
-      </c>
-      <c r="E12">
-        <v>0.82</v>
-      </c>
-      <c r="F12">
-        <v>9.5500000000000007</v>
-      </c>
-      <c r="G12">
-        <v>7.96</v>
-      </c>
-      <c r="H12">
-        <v>1.75</v>
-      </c>
-      <c r="I12">
-        <v>0.17</v>
-      </c>
-      <c r="J12">
-        <v>21.11</v>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" t="s">
+        <v>87</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1391,26 +1946,26 @@
       <c r="C13">
         <v>0</v>
       </c>
-      <c r="D13">
-        <v>0.1</v>
-      </c>
-      <c r="E13">
-        <v>2.9</v>
-      </c>
-      <c r="F13">
-        <v>15.75</v>
-      </c>
-      <c r="G13">
-        <v>2.48</v>
-      </c>
-      <c r="H13">
-        <v>0.24</v>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" t="s">
+        <v>92</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-      <c r="J13">
-        <v>21.5</v>
+      <c r="J13" t="s">
+        <v>93</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -1426,29 +1981,29 @@
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14">
-        <v>0.1</v>
-      </c>
-      <c r="D14">
-        <v>0.24</v>
-      </c>
-      <c r="E14">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="F14">
-        <v>14.26</v>
-      </c>
-      <c r="G14">
-        <v>2.42</v>
-      </c>
-      <c r="H14">
-        <v>0.19</v>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" t="s">
+        <v>97</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
-      <c r="J14">
-        <v>19.98</v>
+      <c r="J14" t="s">
+        <v>98</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -1467,26 +2022,26 @@
       <c r="C15">
         <v>0</v>
       </c>
-      <c r="D15">
-        <v>0.24</v>
-      </c>
-      <c r="E15">
-        <v>2.59</v>
-      </c>
-      <c r="F15">
-        <v>15.25</v>
-      </c>
-      <c r="G15">
-        <v>2.9</v>
-      </c>
-      <c r="H15">
-        <v>0.22</v>
+      <c r="D15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" t="s">
+        <v>101</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
-      <c r="J15">
-        <v>21</v>
+      <c r="J15" t="s">
+        <v>154</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -1508,23 +2063,23 @@
       <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>0.92</v>
-      </c>
-      <c r="F16">
-        <v>11.29</v>
-      </c>
-      <c r="G16">
-        <v>9.14</v>
-      </c>
-      <c r="H16">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="I16">
-        <v>0.17</v>
-      </c>
-      <c r="J16">
-        <v>24.03</v>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" t="s">
+        <v>105</v>
+      </c>
+      <c r="I16" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" t="s">
+        <v>106</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -1540,29 +2095,29 @@
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17">
-        <v>0.27</v>
-      </c>
-      <c r="D17">
-        <v>0.32</v>
-      </c>
-      <c r="E17">
-        <v>1.19</v>
-      </c>
-      <c r="F17">
-        <v>11.24</v>
-      </c>
-      <c r="G17">
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="H17">
-        <v>2.23</v>
-      </c>
-      <c r="I17">
-        <v>0.11</v>
-      </c>
-      <c r="J17">
-        <v>25.1</v>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J17" t="s">
+        <v>112</v>
       </c>
       <c r="K17">
         <v>3</v>
@@ -1581,26 +2136,26 @@
       <c r="C18">
         <v>0</v>
       </c>
-      <c r="D18">
-        <v>0.02</v>
-      </c>
-      <c r="E18">
-        <v>0.24</v>
-      </c>
-      <c r="F18">
-        <v>11.26</v>
-      </c>
-      <c r="G18">
-        <v>8.74</v>
-      </c>
-      <c r="H18">
-        <v>1.1399999999999999</v>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" t="s">
+        <v>116</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
-      <c r="J18">
-        <v>21.52</v>
+      <c r="J18" t="s">
+        <v>117</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -1622,23 +2177,23 @@
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="E19">
-        <v>0.87</v>
-      </c>
-      <c r="F19">
-        <v>9.8699999999999992</v>
-      </c>
-      <c r="G19">
-        <v>9.0399999999999991</v>
-      </c>
-      <c r="H19">
-        <v>1.73</v>
-      </c>
-      <c r="I19">
-        <v>0.03</v>
-      </c>
-      <c r="J19">
-        <v>21.58</v>
+      <c r="E19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" t="s">
+        <v>123</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -1654,29 +2209,29 @@
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20">
-        <v>5.56</v>
-      </c>
-      <c r="D20">
-        <v>19.37</v>
-      </c>
-      <c r="E20">
-        <v>2.31</v>
-      </c>
-      <c r="F20">
-        <v>4.34</v>
-      </c>
-      <c r="G20">
-        <v>0.5</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>24.29</v>
+      <c r="C20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G20" t="s">
+        <v>128</v>
+      </c>
+      <c r="H20" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" t="s">
+        <v>157</v>
+      </c>
+      <c r="J20" t="s">
+        <v>129</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -1692,29 +2247,29 @@
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>0.4</v>
-      </c>
-      <c r="D21">
-        <v>0.79</v>
-      </c>
-      <c r="E21">
-        <v>1.89</v>
-      </c>
-      <c r="F21">
-        <v>12.4</v>
-      </c>
-      <c r="G21">
-        <v>3.98</v>
-      </c>
-      <c r="H21">
-        <v>0.79</v>
-      </c>
-      <c r="I21">
-        <v>0.11</v>
-      </c>
-      <c r="J21">
-        <v>20.13</v>
+      <c r="C21" t="s">
+        <v>130</v>
+      </c>
+      <c r="D21" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G21" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" t="s">
+        <v>135</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -1733,26 +2288,26 @@
       <c r="C22">
         <v>0</v>
       </c>
-      <c r="D22">
-        <v>0.32</v>
-      </c>
-      <c r="E22">
-        <v>2.37</v>
-      </c>
-      <c r="F22">
-        <v>14.63</v>
-      </c>
-      <c r="G22">
-        <v>3.26</v>
-      </c>
-      <c r="H22">
-        <v>0.4</v>
-      </c>
-      <c r="I22">
-        <v>0.03</v>
-      </c>
-      <c r="J22">
-        <v>21.16</v>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G22" t="s">
+        <v>138</v>
+      </c>
+      <c r="H22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" t="s">
+        <v>139</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -1768,29 +2323,29 @@
       <c r="B23">
         <v>1</v>
       </c>
-      <c r="C23">
-        <v>0.08</v>
-      </c>
-      <c r="D23">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="E23">
-        <v>2.34</v>
-      </c>
-      <c r="F23">
-        <v>15.08</v>
-      </c>
-      <c r="G23">
-        <v>5.16</v>
-      </c>
-      <c r="H23">
-        <v>0.32</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>23.44</v>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" t="s">
+        <v>144</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -1809,26 +2364,26 @@
       <c r="C24">
         <v>0</v>
       </c>
-      <c r="D24">
-        <v>0.11</v>
-      </c>
-      <c r="E24">
-        <v>0.96</v>
-      </c>
-      <c r="F24">
-        <v>13.39</v>
-      </c>
-      <c r="G24">
-        <v>6.2</v>
-      </c>
-      <c r="H24">
-        <v>1.58</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>21.81</v>
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" t="s">
+        <v>148</v>
       </c>
       <c r="K24">
         <v>3</v>
@@ -1844,29 +2399,29 @@
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="D25">
-        <v>0.22</v>
-      </c>
-      <c r="E25">
-        <v>2.04</v>
-      </c>
-      <c r="F25">
-        <v>16.78</v>
-      </c>
-      <c r="G25">
-        <v>7.24</v>
-      </c>
-      <c r="H25">
-        <v>0.44</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>27.04</v>
+      <c r="C25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" t="s">
+        <v>157</v>
+      </c>
+      <c r="J25" t="s">
+        <v>153</v>
       </c>
       <c r="K25">
         <v>3</v>
@@ -1875,7 +2430,350 @@
         <v>14</v>
       </c>
     </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" t="s">
+        <v>187</v>
+      </c>
+      <c r="I26" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" t="s">
+        <v>193</v>
+      </c>
+      <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" t="s">
+        <v>188</v>
+      </c>
+      <c r="I27" t="s">
+        <v>158</v>
+      </c>
+      <c r="J27" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="L27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" t="s">
+        <v>178</v>
+      </c>
+      <c r="G28" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" t="s">
+        <v>195</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
+      </c>
+      <c r="L28" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" t="s">
+        <v>173</v>
+      </c>
+      <c r="G29" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" t="s">
+        <v>189</v>
+      </c>
+      <c r="I29" t="s">
+        <v>191</v>
+      </c>
+      <c r="J29" t="s">
+        <v>87</v>
+      </c>
+      <c r="K29">
+        <v>4</v>
+      </c>
+      <c r="L29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" t="s">
+        <v>172</v>
+      </c>
+      <c r="G30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
+      </c>
+      <c r="I30" t="s">
+        <v>157</v>
+      </c>
+      <c r="J30" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" t="s">
+        <v>171</v>
+      </c>
+      <c r="G31" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>157</v>
+      </c>
+      <c r="J31" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31">
+        <v>4</v>
+      </c>
+      <c r="L31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G32" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" t="s">
+        <v>157</v>
+      </c>
+      <c r="J32" t="s">
+        <v>198</v>
+      </c>
+      <c r="K32">
+        <v>4</v>
+      </c>
+      <c r="L32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" t="s">
+        <v>149</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I33" t="s">
+        <v>157</v>
+      </c>
+      <c r="J33" t="s">
+        <v>199</v>
+      </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+      <c r="L33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+      <c r="E34" t="s">
+        <v>168</v>
+      </c>
+      <c r="F34" t="s">
+        <v>169</v>
+      </c>
+      <c r="G34" t="s">
+        <v>186</v>
+      </c>
+      <c r="H34" t="s">
+        <v>190</v>
+      </c>
+      <c r="I34" t="s">
+        <v>157</v>
+      </c>
+      <c r="J34" t="s">
+        <v>200</v>
+      </c>
+      <c r="K34">
+        <v>4</v>
+      </c>
+      <c r="L34" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/primary_data/sieve.xlsx
+++ b/data/primary_data/sieve.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\Abundance_Biomass\abundance_biomass\data\primary_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B667D3-F6E8-4FC3-A283-798877B36FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC93492D-2D75-4B26-A866-201E0DAEDF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{E5E08619-1D5D-4645-A7FE-EF3A7CFA34BE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="339">
   <si>
     <t>site</t>
   </si>
@@ -91,9 +91,6 @@
     <t>5.35</t>
   </si>
   <si>
-    <t>1.3</t>
-  </si>
-  <si>
     <t>0.04</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>0.09</t>
   </si>
   <si>
-    <t>0.6</t>
-  </si>
-  <si>
     <t>1.54</t>
   </si>
   <si>
@@ -163,9 +157,6 @@
     <t>1.53</t>
   </si>
   <si>
-    <t>1.7</t>
-  </si>
-  <si>
     <t>5.76</t>
   </si>
   <si>
@@ -232,9 +223,6 @@
     <t>4.69</t>
   </si>
   <si>
-    <t>25.4</t>
-  </si>
-  <si>
     <t>0.99</t>
   </si>
   <si>
@@ -286,9 +274,6 @@
     <t>21.11</t>
   </si>
   <si>
-    <t>0.1</t>
-  </si>
-  <si>
     <t>2.9</t>
   </si>
   <si>
@@ -301,9 +286,6 @@
     <t>0.24</t>
   </si>
   <si>
-    <t>21.5</t>
-  </si>
-  <si>
     <t>2.43</t>
   </si>
   <si>
@@ -358,9 +340,6 @@
     <t>0.11</t>
   </si>
   <si>
-    <t>25.1</t>
-  </si>
-  <si>
     <t>0.02</t>
   </si>
   <si>
@@ -412,9 +391,6 @@
     <t>24.29</t>
   </si>
   <si>
-    <t>0.4</t>
-  </si>
-  <si>
     <t>0.79</t>
   </si>
   <si>
@@ -484,9 +460,6 @@
     <t>27.04</t>
   </si>
   <si>
-    <t>21.0</t>
-  </si>
-  <si>
     <t>0.15</t>
   </si>
   <si>
@@ -623,6 +596,447 @@
   </si>
   <si>
     <t>15.44</t>
+  </si>
+  <si>
+    <t>october</t>
+  </si>
+  <si>
+    <t xml:space="preserve">october </t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>0.10</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>0.30</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+  <si>
+    <t>2.10</t>
+  </si>
+  <si>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>2.11</t>
+  </si>
+  <si>
+    <t>2.49</t>
+  </si>
+  <si>
+    <t>12.03</t>
+  </si>
+  <si>
+    <t>12.46</t>
+  </si>
+  <si>
+    <t>10.27</t>
+  </si>
+  <si>
+    <t>17.00</t>
+  </si>
+  <si>
+    <t>13.56</t>
+  </si>
+  <si>
+    <t>15.92</t>
+  </si>
+  <si>
+    <t>9.57</t>
+  </si>
+  <si>
+    <t>8.48</t>
+  </si>
+  <si>
+    <t>8.61</t>
+  </si>
+  <si>
+    <t>6.18</t>
+  </si>
+  <si>
+    <t>1.90</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>5.82</t>
+  </si>
+  <si>
+    <t>3.87</t>
+  </si>
+  <si>
+    <t>6.41</t>
+  </si>
+  <si>
+    <t>0.50</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>2.57</t>
+  </si>
+  <si>
+    <t>21.89</t>
+  </si>
+  <si>
+    <t>21.35</t>
+  </si>
+  <si>
+    <t>18.27</t>
+  </si>
+  <si>
+    <t>20.40</t>
+  </si>
+  <si>
+    <t>18.85</t>
+  </si>
+  <si>
+    <t>19.96</t>
+  </si>
+  <si>
+    <t>15.62</t>
+  </si>
+  <si>
+    <t>21.57</t>
+  </si>
+  <si>
+    <t>december</t>
+  </si>
+  <si>
+    <t xml:space="preserve">december </t>
+  </si>
+  <si>
+    <t>30.79</t>
+  </si>
+  <si>
+    <t>32.24</t>
+  </si>
+  <si>
+    <t>22.91</t>
+  </si>
+  <si>
+    <t>25.48</t>
+  </si>
+  <si>
+    <t>20.15</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>0.23</t>
+  </si>
+  <si>
+    <t>3.37</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>5.69</t>
+  </si>
+  <si>
+    <t>11.00</t>
+  </si>
+  <si>
+    <t>7.74</t>
+  </si>
+  <si>
+    <t>13.02</t>
+  </si>
+  <si>
+    <t>15.72</t>
+  </si>
+  <si>
+    <t>27.74</t>
+  </si>
+  <si>
+    <t>15.55</t>
+  </si>
+  <si>
+    <t>25.17</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>0.40</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>0.60</t>
+  </si>
+  <si>
+    <t>2.90</t>
+  </si>
+  <si>
+    <t>1.30</t>
+  </si>
+  <si>
+    <t>18.02</t>
+  </si>
+  <si>
+    <t>21.00</t>
+  </si>
+  <si>
+    <t>25.40</t>
+  </si>
+  <si>
+    <t>21.50</t>
+  </si>
+  <si>
+    <t>25.10</t>
+  </si>
+  <si>
+    <t>january</t>
+  </si>
+  <si>
+    <t>24.07</t>
+  </si>
+  <si>
+    <t>20.30</t>
+  </si>
+  <si>
+    <t>20.89</t>
+  </si>
+  <si>
+    <t>12.89</t>
+  </si>
+  <si>
+    <t>22.00</t>
+  </si>
+  <si>
+    <t>17.66</t>
+  </si>
+  <si>
+    <t>16.47</t>
+  </si>
+  <si>
+    <t>20.96</t>
+  </si>
+  <si>
+    <t>14.97</t>
+  </si>
+  <si>
+    <t>0.20</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>1.83</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>1.71</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>8.37</t>
+  </si>
+  <si>
+    <t>11.56</t>
+  </si>
+  <si>
+    <t>9.15</t>
+  </si>
+  <si>
+    <t>15.51</t>
+  </si>
+  <si>
+    <t>18.55</t>
+  </si>
+  <si>
+    <t>11.10</t>
+  </si>
+  <si>
+    <t>10.34</t>
+  </si>
+  <si>
+    <t>10.41</t>
+  </si>
+  <si>
+    <t>12.27</t>
+  </si>
+  <si>
+    <t>7.63</t>
+  </si>
+  <si>
+    <t>6.36</t>
+  </si>
+  <si>
+    <t>7.27</t>
+  </si>
+  <si>
+    <t>1.05</t>
+  </si>
+  <si>
+    <t>5.20</t>
+  </si>
+  <si>
+    <t>6.55</t>
+  </si>
+  <si>
+    <t>4.01</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>1.88</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>3.36</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>2.82</t>
+  </si>
+  <si>
+    <t>15.81</t>
+  </si>
+  <si>
+    <t>12.20</t>
+  </si>
+  <si>
+    <t>7.17</t>
+  </si>
+  <si>
+    <t>14.41</t>
+  </si>
+  <si>
+    <t>15.58</t>
+  </si>
+  <si>
+    <t>15.11</t>
+  </si>
+  <si>
+    <t>6.42</t>
+  </si>
+  <si>
+    <t>4.21</t>
+  </si>
+  <si>
+    <t>13.53</t>
+  </si>
+  <si>
+    <t>5.11</t>
+  </si>
+  <si>
+    <t>2.00</t>
+  </si>
+  <si>
+    <t>1.56</t>
+  </si>
+  <si>
+    <t>4.62</t>
+  </si>
+  <si>
+    <t>5.24</t>
+  </si>
+  <si>
+    <t>10.75</t>
+  </si>
+  <si>
+    <t>5.87</t>
+  </si>
+  <si>
+    <t>7.39</t>
+  </si>
+  <si>
+    <t>0.63</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>0.56</t>
+  </si>
+  <si>
+    <t>22.45</t>
+  </si>
+  <si>
+    <t>17.24</t>
+  </si>
+  <si>
+    <t>15.04</t>
+  </si>
+  <si>
+    <t>18.36</t>
+  </si>
+  <si>
+    <t>16.66</t>
+  </si>
+  <si>
+    <t>17.45</t>
+  </si>
+  <si>
+    <t>20.83</t>
+  </si>
+  <si>
+    <t>22.59</t>
+  </si>
+  <si>
+    <t>29.90</t>
+  </si>
+  <si>
+    <t>february</t>
+  </si>
+  <si>
+    <t xml:space="preserve">february </t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -1469,7 +1883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B1941EC-5D36-4969-84B5-0B119B8E4EB5}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -1478,9 +1892,10 @@
     <col min="8" max="8" width="11.5703125" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" customWidth="1"/>
     <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1517,8 +1932,11 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1541,13 +1959,13 @@
         <v>22</v>
       </c>
       <c r="H2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -1555,8 +1973,11 @@
       <c r="L2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1564,28 +1985,28 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -1593,8 +2014,11 @@
       <c r="L3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1605,25 +2029,25 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -1631,8 +2055,11 @@
       <c r="L4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1640,28 +2067,28 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>42</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
         <v>43</v>
-      </c>
-      <c r="H5" t="s">
-        <v>44</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5" t="s">
-        <v>45</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1669,8 +2096,11 @@
       <c r="L5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1678,28 +2108,28 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" t="s">
         <v>46</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>48</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" t="s">
         <v>49</v>
-      </c>
-      <c r="G6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -1707,8 +2137,11 @@
       <c r="L6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1716,28 +2149,28 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="D7" t="s">
+      <c r="G7" t="s">
         <v>54</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
         <v>55</v>
       </c>
-      <c r="F7" t="s">
+      <c r="J7" t="s">
         <v>56</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" t="s">
-        <v>59</v>
       </c>
       <c r="K7">
         <v>1</v>
@@ -1745,8 +2178,11 @@
       <c r="L7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1754,28 +2190,28 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" t="s">
         <v>60</v>
       </c>
-      <c r="F8" t="s">
+      <c r="I8" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" t="s">
         <v>61</v>
-      </c>
-      <c r="G8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>64</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -1783,8 +2219,11 @@
       <c r="L8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1792,28 +2231,28 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" t="s">
         <v>65</v>
       </c>
-      <c r="D9" t="s">
+      <c r="G9" t="s">
         <v>66</v>
-      </c>
-      <c r="E9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" t="s">
-        <v>69</v>
       </c>
       <c r="H9" t="s">
         <v>18</v>
       </c>
-      <c r="I9">
-        <v>0</v>
+      <c r="I9" t="s">
+        <v>148</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>259</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -1821,8 +2260,11 @@
       <c r="L9" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1830,28 +2272,28 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" t="s">
+        <v>148</v>
+      </c>
+      <c r="J10" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>75</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1859,8 +2301,11 @@
       <c r="L10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1868,28 +2313,28 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s">
         <v>76</v>
       </c>
-      <c r="E11" t="s">
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" t="s">
         <v>77</v>
-      </c>
-      <c r="F11" t="s">
-        <v>78</v>
-      </c>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" t="s">
-        <v>81</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -1897,8 +2342,11 @@
       <c r="L11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1906,28 +2354,28 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I12" t="s">
         <v>82</v>
       </c>
-      <c r="F12" t="s">
+      <c r="J12" t="s">
         <v>83</v>
-      </c>
-      <c r="G12" t="s">
-        <v>84</v>
-      </c>
-      <c r="H12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I12" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" t="s">
-        <v>87</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1935,37 +2383,40 @@
       <c r="L12" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M12">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13">
-        <v>0</v>
+      <c r="C13" t="s">
+        <v>148</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>195</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>255</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>92</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="I13" t="s">
+        <v>148</v>
       </c>
       <c r="J13" t="s">
-        <v>93</v>
+        <v>260</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -1973,8 +2424,11 @@
       <c r="L13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M13">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1982,28 +2436,28 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
         <v>88</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14" t="s">
         <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" t="s">
-        <v>98</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -2011,37 +2465,40 @@
       <c r="L14" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15">
-        <v>0</v>
+      <c r="C15" t="s">
+        <v>148</v>
       </c>
       <c r="D15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
+        <v>95</v>
+      </c>
+      <c r="I15" t="s">
+        <v>148</v>
       </c>
       <c r="J15" t="s">
-        <v>154</v>
+        <v>258</v>
       </c>
       <c r="K15">
         <v>2</v>
@@ -2049,37 +2506,40 @@
       <c r="L15" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M15">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
+      <c r="C16" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" t="s">
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="J16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -2087,8 +2547,11 @@
       <c r="L16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M16">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -2096,28 +2559,28 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
         <v>20</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J17" t="s">
-        <v>112</v>
+        <v>261</v>
       </c>
       <c r="K17">
         <v>3</v>
@@ -2125,37 +2588,40 @@
       <c r="L17" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M17">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
-      <c r="C18">
-        <v>0</v>
+      <c r="C18" t="s">
+        <v>148</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G18" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
+        <v>109</v>
+      </c>
+      <c r="I18" t="s">
+        <v>148</v>
       </c>
       <c r="J18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -2163,37 +2629,40 @@
       <c r="L18" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M18">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>7</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
+      <c r="C19" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G19" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K19">
         <v>3</v>
@@ -2201,8 +2670,11 @@
       <c r="L19" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M19">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2210,28 +2682,28 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F20" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G20" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I20" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J20" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -2239,8 +2711,11 @@
       <c r="L20" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M20">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2248,28 +2723,28 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G21" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J21" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -2277,37 +2752,40 @@
       <c r="L21" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M21">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
       <c r="B22">
         <v>3</v>
       </c>
-      <c r="C22">
-        <v>0</v>
+      <c r="C22" t="s">
+        <v>148</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G22" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
+        <v>252</v>
       </c>
       <c r="I22" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="J22" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -2315,8 +2793,11 @@
       <c r="L22" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M22">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -2324,28 +2805,28 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E23" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F23" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I23" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J23" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="K23">
         <v>3</v>
@@ -2353,37 +2834,40 @@
       <c r="L23" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M23">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24">
-        <v>0</v>
+      <c r="C24" t="s">
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G24" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I24" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J24" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K24">
         <v>3</v>
@@ -2391,8 +2875,11 @@
       <c r="L24" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M24">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -2400,28 +2887,28 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D25" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G25" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="H25" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I25" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J25" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="K25">
         <v>3</v>
@@ -2429,8 +2916,11 @@
       <c r="L25" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M25">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -2438,37 +2928,40 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="F26" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G26" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H26" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I26" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="J26" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="K26">
         <v>4</v>
       </c>
       <c r="L26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M26">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -2476,37 +2969,40 @@
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="F27" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G27" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H27" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="J27" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="K27">
         <v>4</v>
       </c>
       <c r="L27" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M27">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -2514,37 +3010,40 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F28" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G28" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J28" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="K28">
         <v>4</v>
       </c>
       <c r="L28" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M28">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2552,37 +3051,40 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E29" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" t="s">
         <v>164</v>
       </c>
-      <c r="F29" t="s">
-        <v>173</v>
-      </c>
       <c r="G29" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29" t="s">
         <v>180</v>
       </c>
-      <c r="H29" t="s">
-        <v>189</v>
-      </c>
       <c r="I29" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="J29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K29">
         <v>4</v>
       </c>
       <c r="L29" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M29">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -2590,37 +3092,40 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F30" t="s">
+        <v>163</v>
+      </c>
+      <c r="G30" t="s">
         <v>172</v>
-      </c>
-      <c r="G30" t="s">
-        <v>181</v>
       </c>
       <c r="H30" t="s">
         <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J30" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K30">
         <v>4</v>
       </c>
       <c r="L30" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M30">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2628,37 +3133,40 @@
         <v>3</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="F31" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H31" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I31" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J31" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="K31">
         <v>4</v>
       </c>
       <c r="L31" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M31">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>9</v>
       </c>
@@ -2666,37 +3174,40 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D32" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E32" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F32" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G32" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H32" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J32" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="K32">
         <v>4</v>
       </c>
       <c r="L32" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M32">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>9</v>
       </c>
@@ -2704,37 +3215,40 @@
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G33" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I33" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J33" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="K33">
         <v>4</v>
       </c>
       <c r="L33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="M33">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>9</v>
       </c>
@@ -2742,34 +3256,1390 @@
         <v>3</v>
       </c>
       <c r="C34" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D34" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E34" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H34" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I34" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="J34" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="K34">
         <v>4</v>
       </c>
       <c r="L34" t="s">
+        <v>183</v>
+      </c>
+      <c r="M34">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" t="s">
+        <v>198</v>
+      </c>
+      <c r="F35" t="s">
+        <v>213</v>
+      </c>
+      <c r="G35" t="s">
+        <v>214</v>
+      </c>
+      <c r="H35" t="s">
+        <v>223</v>
+      </c>
+      <c r="I35" t="s">
+        <v>87</v>
+      </c>
+      <c r="J35" t="s">
+        <v>231</v>
+      </c>
+      <c r="K35">
+        <v>5</v>
+      </c>
+      <c r="L35" t="s">
         <v>192</v>
+      </c>
+      <c r="M35">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36">
+        <v>2</v>
+      </c>
+      <c r="C36" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" t="s">
+        <v>199</v>
+      </c>
+      <c r="F36" t="s">
+        <v>54</v>
+      </c>
+      <c r="G36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" t="s">
+        <v>105</v>
+      </c>
+      <c r="J36" t="s">
+        <v>230</v>
+      </c>
+      <c r="K36">
+        <v>5</v>
+      </c>
+      <c r="L36" t="s">
+        <v>193</v>
+      </c>
+      <c r="M36">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" t="s">
+        <v>215</v>
+      </c>
+      <c r="H37" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" t="s">
+        <v>222</v>
+      </c>
+      <c r="J37" t="s">
+        <v>229</v>
+      </c>
+      <c r="K37">
+        <v>5</v>
+      </c>
+      <c r="L37" t="s">
+        <v>192</v>
+      </c>
+      <c r="M37">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" t="s">
+        <v>211</v>
+      </c>
+      <c r="G38" t="s">
+        <v>216</v>
+      </c>
+      <c r="H38" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" t="s">
+        <v>148</v>
+      </c>
+      <c r="J38" t="s">
+        <v>228</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+      <c r="L38" t="s">
+        <v>192</v>
+      </c>
+      <c r="M38">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E39" t="s">
+        <v>201</v>
+      </c>
+      <c r="F39" t="s">
+        <v>210</v>
+      </c>
+      <c r="G39" t="s">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s">
+        <v>151</v>
+      </c>
+      <c r="I39" t="s">
+        <v>23</v>
+      </c>
+      <c r="J39" t="s">
+        <v>257</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
+      </c>
+      <c r="L39" t="s">
+        <v>192</v>
+      </c>
+      <c r="M39">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40">
+        <v>3</v>
+      </c>
+      <c r="C40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" t="s">
+        <v>196</v>
+      </c>
+      <c r="E40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" t="s">
+        <v>209</v>
+      </c>
+      <c r="G40" t="s">
+        <v>217</v>
+      </c>
+      <c r="H40" t="s">
+        <v>222</v>
+      </c>
+      <c r="I40" t="s">
+        <v>148</v>
+      </c>
+      <c r="J40" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
+      </c>
+      <c r="L40" t="s">
+        <v>192</v>
+      </c>
+      <c r="M40">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
+        <v>208</v>
+      </c>
+      <c r="G41" t="s">
+        <v>218</v>
+      </c>
+      <c r="H41" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41" t="s">
+        <v>148</v>
+      </c>
+      <c r="J41" t="s">
+        <v>226</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41" t="s">
+        <v>192</v>
+      </c>
+      <c r="M41">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" t="s">
+        <v>195</v>
+      </c>
+      <c r="E42" t="s">
+        <v>204</v>
+      </c>
+      <c r="F42" t="s">
+        <v>207</v>
+      </c>
+      <c r="G42" t="s">
+        <v>219</v>
+      </c>
+      <c r="H42" t="s">
+        <v>51</v>
+      </c>
+      <c r="I42" t="s">
+        <v>148</v>
+      </c>
+      <c r="J42" t="s">
+        <v>225</v>
+      </c>
+      <c r="K42">
+        <v>5</v>
+      </c>
+      <c r="L42" t="s">
+        <v>192</v>
+      </c>
+      <c r="M42">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" t="s">
+        <v>206</v>
+      </c>
+      <c r="G43" t="s">
+        <v>220</v>
+      </c>
+      <c r="H43" t="s">
+        <v>150</v>
+      </c>
+      <c r="I43" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" t="s">
+        <v>224</v>
+      </c>
+      <c r="K43">
+        <v>5</v>
+      </c>
+      <c r="L43" t="s">
+        <v>192</v>
+      </c>
+      <c r="M43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" t="s">
+        <v>63</v>
+      </c>
+      <c r="E44" t="s">
+        <v>63</v>
+      </c>
+      <c r="F44" t="s">
+        <v>250</v>
+      </c>
+      <c r="G44" t="s">
+        <v>241</v>
+      </c>
+      <c r="H44" t="s">
+        <v>151</v>
+      </c>
+      <c r="I44" t="s">
+        <v>148</v>
+      </c>
+      <c r="J44" t="s">
+        <v>234</v>
+      </c>
+      <c r="K44">
+        <v>6</v>
+      </c>
+      <c r="L44" t="s">
+        <v>232</v>
+      </c>
+      <c r="M44">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" t="s">
+        <v>146</v>
+      </c>
+      <c r="F45" t="s">
+        <v>249</v>
+      </c>
+      <c r="G45" t="s">
+        <v>216</v>
+      </c>
+      <c r="H45" t="s">
+        <v>55</v>
+      </c>
+      <c r="I45" t="s">
+        <v>148</v>
+      </c>
+      <c r="J45" t="s">
+        <v>188</v>
+      </c>
+      <c r="K45">
+        <v>6</v>
+      </c>
+      <c r="L45" t="s">
+        <v>232</v>
+      </c>
+      <c r="M45">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E46" t="s">
+        <v>240</v>
+      </c>
+      <c r="F46" t="s">
+        <v>248</v>
+      </c>
+      <c r="G46" t="s">
+        <v>242</v>
+      </c>
+      <c r="H46" t="s">
+        <v>240</v>
+      </c>
+      <c r="I46" t="s">
+        <v>147</v>
+      </c>
+      <c r="J46" t="s">
+        <v>235</v>
+      </c>
+      <c r="K46">
+        <v>6</v>
+      </c>
+      <c r="L46" t="s">
+        <v>232</v>
+      </c>
+      <c r="M46">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>240</v>
+      </c>
+      <c r="D47" t="s">
+        <v>251</v>
+      </c>
+      <c r="E47" t="s">
+        <v>251</v>
+      </c>
+      <c r="F47" t="s">
+        <v>247</v>
+      </c>
+      <c r="G47" t="s">
+        <v>243</v>
+      </c>
+      <c r="H47" t="s">
+        <v>48</v>
+      </c>
+      <c r="I47" t="s">
+        <v>106</v>
+      </c>
+      <c r="J47" t="s">
+        <v>236</v>
+      </c>
+      <c r="K47">
+        <v>6</v>
+      </c>
+      <c r="L47" t="s">
+        <v>233</v>
+      </c>
+      <c r="M47">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" t="s">
+        <v>221</v>
+      </c>
+      <c r="F48" t="s">
+        <v>246</v>
+      </c>
+      <c r="G48" t="s">
+        <v>244</v>
+      </c>
+      <c r="H48" t="s">
+        <v>51</v>
+      </c>
+      <c r="I48" t="s">
+        <v>148</v>
+      </c>
+      <c r="J48" t="s">
+        <v>237</v>
+      </c>
+      <c r="K48">
+        <v>6</v>
+      </c>
+      <c r="L48" t="s">
+        <v>232</v>
+      </c>
+      <c r="M48">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" t="s">
+        <v>252</v>
+      </c>
+      <c r="F49" t="s">
+        <v>107</v>
+      </c>
+      <c r="G49" t="s">
+        <v>245</v>
+      </c>
+      <c r="H49" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" t="s">
+        <v>148</v>
+      </c>
+      <c r="J49" t="s">
+        <v>238</v>
+      </c>
+      <c r="K49">
+        <v>6</v>
+      </c>
+      <c r="L49" t="s">
+        <v>232</v>
+      </c>
+      <c r="M49">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" t="s">
+        <v>274</v>
+      </c>
+      <c r="E50" t="s">
+        <v>275</v>
+      </c>
+      <c r="F50" t="s">
+        <v>290</v>
+      </c>
+      <c r="G50" t="s">
+        <v>291</v>
+      </c>
+      <c r="H50" t="s">
+        <v>298</v>
+      </c>
+      <c r="I50" t="s">
+        <v>182</v>
+      </c>
+      <c r="J50" t="s">
+        <v>263</v>
+      </c>
+      <c r="K50">
+        <v>7</v>
+      </c>
+      <c r="L50" t="s">
+        <v>262</v>
+      </c>
+      <c r="M50">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>276</v>
+      </c>
+      <c r="F51" t="s">
+        <v>289</v>
+      </c>
+      <c r="G51" t="s">
+        <v>292</v>
+      </c>
+      <c r="H51" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" t="s">
+        <v>141</v>
+      </c>
+      <c r="J51" t="s">
+        <v>264</v>
+      </c>
+      <c r="K51">
+        <v>7</v>
+      </c>
+      <c r="L51" t="s">
+        <v>262</v>
+      </c>
+      <c r="M51">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" t="s">
+        <v>277</v>
+      </c>
+      <c r="F52" t="s">
+        <v>288</v>
+      </c>
+      <c r="G52" t="s">
+        <v>293</v>
+      </c>
+      <c r="H52" t="s">
+        <v>202</v>
+      </c>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>265</v>
+      </c>
+      <c r="K52">
+        <v>7</v>
+      </c>
+      <c r="L52" t="s">
+        <v>262</v>
+      </c>
+      <c r="M52">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>148</v>
+      </c>
+      <c r="D53" t="s">
+        <v>148</v>
+      </c>
+      <c r="E53" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" t="s">
+        <v>287</v>
+      </c>
+      <c r="G53" t="s">
+        <v>153</v>
+      </c>
+      <c r="H53" t="s">
+        <v>141</v>
+      </c>
+      <c r="I53" t="s">
+        <v>148</v>
+      </c>
+      <c r="J53" t="s">
+        <v>266</v>
+      </c>
+      <c r="K53">
+        <v>7</v>
+      </c>
+      <c r="L53" t="s">
+        <v>262</v>
+      </c>
+      <c r="M53">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>8</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E54" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" t="s">
+        <v>286</v>
+      </c>
+      <c r="G54" t="s">
+        <v>29</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" t="s">
+        <v>148</v>
+      </c>
+      <c r="J54" t="s">
+        <v>267</v>
+      </c>
+      <c r="K54">
+        <v>7</v>
+      </c>
+      <c r="L54" t="s">
+        <v>262</v>
+      </c>
+      <c r="M54">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>8</v>
+      </c>
+      <c r="B55">
+        <v>3</v>
+      </c>
+      <c r="C55" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" t="s">
+        <v>273</v>
+      </c>
+      <c r="E55" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" t="s">
+        <v>285</v>
+      </c>
+      <c r="G55" t="s">
+        <v>294</v>
+      </c>
+      <c r="H55" t="s">
+        <v>148</v>
+      </c>
+      <c r="I55" t="s">
+        <v>148</v>
+      </c>
+      <c r="J55" t="s">
+        <v>268</v>
+      </c>
+      <c r="K55">
+        <v>7</v>
+      </c>
+      <c r="L55" t="s">
+        <v>262</v>
+      </c>
+      <c r="M55">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" t="s">
+        <v>195</v>
+      </c>
+      <c r="E56" t="s">
+        <v>273</v>
+      </c>
+      <c r="F56" t="s">
+        <v>284</v>
+      </c>
+      <c r="G56" t="s">
+        <v>295</v>
+      </c>
+      <c r="H56" t="s">
+        <v>221</v>
+      </c>
+      <c r="I56" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" t="s">
+        <v>269</v>
+      </c>
+      <c r="K56">
+        <v>7</v>
+      </c>
+      <c r="L56" t="s">
+        <v>262</v>
+      </c>
+      <c r="M56">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" t="s">
+        <v>280</v>
+      </c>
+      <c r="F57" t="s">
+        <v>283</v>
+      </c>
+      <c r="G57" t="s">
+        <v>296</v>
+      </c>
+      <c r="H57" t="s">
+        <v>144</v>
+      </c>
+      <c r="I57" t="s">
+        <v>148</v>
+      </c>
+      <c r="J57" t="s">
+        <v>270</v>
+      </c>
+      <c r="K57">
+        <v>7</v>
+      </c>
+      <c r="L57" t="s">
+        <v>262</v>
+      </c>
+      <c r="M57">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58" t="s">
+        <v>272</v>
+      </c>
+      <c r="D58" t="s">
+        <v>87</v>
+      </c>
+      <c r="E58" t="s">
+        <v>281</v>
+      </c>
+      <c r="F58" t="s">
+        <v>282</v>
+      </c>
+      <c r="G58" t="s">
+        <v>297</v>
+      </c>
+      <c r="H58" t="s">
+        <v>51</v>
+      </c>
+      <c r="I58" t="s">
+        <v>148</v>
+      </c>
+      <c r="J58" t="s">
+        <v>271</v>
+      </c>
+      <c r="K58">
+        <v>7</v>
+      </c>
+      <c r="L58" t="s">
+        <v>262</v>
+      </c>
+      <c r="M58">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>48</v>
+      </c>
+      <c r="D59" t="s">
+        <v>301</v>
+      </c>
+      <c r="E59" t="s">
+        <v>303</v>
+      </c>
+      <c r="F59" t="s">
+        <v>313</v>
+      </c>
+      <c r="G59" t="s">
+        <v>319</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="I59" t="s">
+        <v>148</v>
+      </c>
+      <c r="J59" t="s">
+        <v>328</v>
+      </c>
+      <c r="K59">
+        <v>8</v>
+      </c>
+      <c r="L59" t="s">
+        <v>336</v>
+      </c>
+      <c r="M59">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>299</v>
+      </c>
+      <c r="D60" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60" t="s">
+        <v>302</v>
+      </c>
+      <c r="F60" t="s">
+        <v>314</v>
+      </c>
+      <c r="G60" t="s">
+        <v>320</v>
+      </c>
+      <c r="H60" t="s">
+        <v>180</v>
+      </c>
+      <c r="I60" t="s">
+        <v>148</v>
+      </c>
+      <c r="J60" t="s">
+        <v>329</v>
+      </c>
+      <c r="K60">
+        <v>8</v>
+      </c>
+      <c r="L60" t="s">
+        <v>336</v>
+      </c>
+      <c r="M60">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
+        <v>315</v>
+      </c>
+      <c r="G61" t="s">
+        <v>316</v>
+      </c>
+      <c r="H61" t="s">
+        <v>326</v>
+      </c>
+      <c r="I61" t="s">
+        <v>106</v>
+      </c>
+      <c r="J61" t="s">
+        <v>327</v>
+      </c>
+      <c r="K61">
+        <v>8</v>
+      </c>
+      <c r="L61" t="s">
+        <v>336</v>
+      </c>
+      <c r="M61">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" t="s">
+        <v>148</v>
+      </c>
+      <c r="E62" t="s">
+        <v>304</v>
+      </c>
+      <c r="F62" t="s">
+        <v>312</v>
+      </c>
+      <c r="G62" t="s">
+        <v>318</v>
+      </c>
+      <c r="H62" t="s">
+        <v>82</v>
+      </c>
+      <c r="I62" t="s">
+        <v>106</v>
+      </c>
+      <c r="J62" t="s">
+        <v>332</v>
+      </c>
+      <c r="K62">
+        <v>8</v>
+      </c>
+      <c r="L62" t="s">
+        <v>336</v>
+      </c>
+      <c r="M62">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" t="s">
+        <v>62</v>
+      </c>
+      <c r="F63" t="s">
+        <v>310</v>
+      </c>
+      <c r="G63" t="s">
+        <v>281</v>
+      </c>
+      <c r="H63" t="s">
+        <v>87</v>
+      </c>
+      <c r="I63" t="s">
+        <v>106</v>
+      </c>
+      <c r="J63" t="s">
+        <v>331</v>
+      </c>
+      <c r="K63">
+        <v>8</v>
+      </c>
+      <c r="L63" t="s">
+        <v>336</v>
+      </c>
+      <c r="M63">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64">
+        <v>3</v>
+      </c>
+      <c r="C64" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" t="s">
+        <v>101</v>
+      </c>
+      <c r="F64" t="s">
+        <v>311</v>
+      </c>
+      <c r="G64" t="s">
+        <v>317</v>
+      </c>
+      <c r="H64" t="s">
+        <v>181</v>
+      </c>
+      <c r="I64" t="s">
+        <v>148</v>
+      </c>
+      <c r="J64" t="s">
+        <v>330</v>
+      </c>
+      <c r="K64">
+        <v>8</v>
+      </c>
+      <c r="L64" t="s">
+        <v>336</v>
+      </c>
+      <c r="M64">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" t="s">
+        <v>105</v>
+      </c>
+      <c r="E65" t="s">
+        <v>198</v>
+      </c>
+      <c r="F65" t="s">
+        <v>309</v>
+      </c>
+      <c r="G65" t="s">
+        <v>321</v>
+      </c>
+      <c r="H65" t="s">
+        <v>280</v>
+      </c>
+      <c r="I65" t="s">
+        <v>182</v>
+      </c>
+      <c r="J65" t="s">
+        <v>333</v>
+      </c>
+      <c r="K65">
+        <v>8</v>
+      </c>
+      <c r="L65" t="s">
+        <v>336</v>
+      </c>
+      <c r="M65">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>272</v>
+      </c>
+      <c r="D66" t="s">
+        <v>60</v>
+      </c>
+      <c r="E66" t="s">
+        <v>305</v>
+      </c>
+      <c r="F66" t="s">
+        <v>308</v>
+      </c>
+      <c r="G66" t="s">
+        <v>322</v>
+      </c>
+      <c r="H66" t="s">
+        <v>325</v>
+      </c>
+      <c r="I66" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" t="s">
+        <v>334</v>
+      </c>
+      <c r="K66">
+        <v>8</v>
+      </c>
+      <c r="L66" t="s">
+        <v>337</v>
+      </c>
+      <c r="M66">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67">
+        <v>3</v>
+      </c>
+      <c r="C67" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" t="s">
+        <v>300</v>
+      </c>
+      <c r="E67" t="s">
+        <v>306</v>
+      </c>
+      <c r="F67" t="s">
+        <v>307</v>
+      </c>
+      <c r="G67" t="s">
+        <v>323</v>
+      </c>
+      <c r="H67" t="s">
+        <v>324</v>
+      </c>
+      <c r="I67" t="s">
+        <v>148</v>
+      </c>
+      <c r="J67" t="s">
+        <v>335</v>
+      </c>
+      <c r="K67">
+        <v>8</v>
+      </c>
+      <c r="L67" t="s">
+        <v>336</v>
+      </c>
+      <c r="M67">
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
